--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487856_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487856_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5436</v>
+        <v>6.466</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9761</v>
+        <v>4.9278</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5675</v>
+        <v>1.5381</v>
       </c>
       <c r="G2" t="n">
         <v>2.9861</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3192</v>
+        <v>0.2416</v>
       </c>
       <c r="T2" t="n">
-        <v>1.124</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1951</v>
+        <v>0.1658</v>
       </c>
       <c r="V2" t="n">
         <v>2.4058</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4428</v>
+        <v>4.7811</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5254</v>
+        <v>2.8049</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9174</v>
+        <v>1.9761</v>
       </c>
       <c r="G3" t="n">
         <v>3.4511</v>
@@ -688,13 +688,13 @@
         <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1696</v>
+        <v>0.5079</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1833</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.353</v>
+        <v>0.4117</v>
       </c>
       <c r="V3" t="n">
         <v>1.2383</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>A. INFANTE GUTIERREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0146</v>
+        <v>2.2719</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2533</v>
+        <v>-0.5528</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7613</v>
+        <v>2.8247</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9871</v>
+        <v>3.0139</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0939</v>
+        <v>2.1771</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0809</v>
+        <v>0.8368</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3995</v>
+        <v>2.3037</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1063</v>
+        <v>1.1853</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2932</v>
+        <v>1.1185</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4124</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2002</v>
+        <v>0.9918</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2123</v>
+        <v>-0.2817</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8325</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2081</v>
+        <v>-3.3299</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0406</v>
+        <v>2.0812</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3118</v>
+        <v>0.0396</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0619</v>
+        <v>-0.1105</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2499</v>
+        <v>0.1501</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1168</v>
+        <v>0.467</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X4" t="n">
         <v>-0.1168</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. INFANTE GUTIERREZ</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8734</v>
+        <v>1.5273</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5109</v>
+        <v>0.8247</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3843</v>
+        <v>0.7026</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0139</v>
+        <v>0.9871</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1771</v>
+        <v>-0.0939</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8368</v>
+        <v>1.0809</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3037</v>
+        <v>1.3995</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1853</v>
+        <v>0.1063</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1185</v>
+        <v>1.2932</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7102000000000001</v>
+        <v>-0.4124</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9918</v>
+        <v>-0.2002</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2817</v>
+        <v>-0.2123</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.3299</v>
+        <v>-0.2081</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0812</v>
+        <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3588</v>
+        <v>-0.1755</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.3667</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2903</v>
+        <v>0.1912</v>
       </c>
       <c r="V5" t="n">
-        <v>0.467</v>
+        <v>-0.1168</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-0.1168</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1175</v>
+        <v>1.2921</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2073</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9102</v>
+        <v>0.7634</v>
       </c>
       <c r="G6" t="n">
         <v>0.2064</v>
@@ -922,13 +922,13 @@
         <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>0.216</v>
+        <v>0.3906</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4443</v>
+        <v>-0.1228</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6603</v>
+        <v>0.5135</v>
       </c>
       <c r="V6" t="n">
         <v>0.0708</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. SALL</t>
+          <t>A. PLITZUWEIT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4177</v>
+        <v>0.8431</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.411</v>
+        <v>0.5165</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8287</v>
+        <v>0.3266</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0959</v>
+        <v>0.1465</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0348</v>
+        <v>0.4714</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1306</v>
+        <v>-0.3249</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6836</v>
+        <v>0.8325</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8796</v>
+        <v>0.341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1959</v>
+        <v>0.4915</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7795</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8448</v>
+        <v>0.1304</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0653</v>
+        <v>-0.8164</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>-1.4568</v>
       </c>
       <c r="R7" t="n">
         <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5924</v>
+        <v>-0.1949</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5401</v>
+        <v>-0.0266</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0523</v>
+        <v>-0.1683</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3538</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8137</v>
+        <v>1.1675</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4599</v>
+        <v>-0.276</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PLITZUWEIT</t>
+          <t>P. SALL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.278</v>
+        <v>0.0902</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0193</v>
+        <v>-1.7091</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2973</v>
+        <v>1.7993</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1465</v>
+        <v>0.0959</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4714</v>
+        <v>-0.0348</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3249</v>
+        <v>0.1306</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8325</v>
+        <v>-0.6836</v>
       </c>
       <c r="K8" t="n">
-        <v>0.341</v>
+        <v>-0.8796</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4915</v>
+        <v>0.1959</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6860000000000001</v>
+        <v>0.7795</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1304</v>
+        <v>0.8448</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8164</v>
+        <v>-0.0653</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.4568</v>
+        <v>-2.0812</v>
       </c>
       <c r="R8" t="n">
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.76</v>
+        <v>0.2649</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5624</v>
+        <v>0.242</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1976</v>
+        <v>0.0229</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.3538</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.276</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1933</v>
+        <v>-1.0106</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0675</v>
+        <v>-1.0022</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1259</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7373</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.456</v>
+        <v>-0.2734</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3915</v>
+        <v>-0.3262</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0646</v>
+        <v>0.0529</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7567</v>
+        <v>-2.5219</v>
       </c>
       <c r="E10" t="n">
         <v>-2.8532</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0965</v>
+        <v>0.3314</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0258</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1574</v>
+        <v>-0.9225</v>
       </c>
       <c r="T10" t="n">
         <v>-0.5219</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6354</v>
+        <v>-0.4005</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1168</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9141</v>
+        <v>-3.3528</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4507</v>
+        <v>-4.7425</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5365</v>
+        <v>1.3897</v>
       </c>
       <c r="G11" t="n">
         <v>-4.2358</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.927</v>
+        <v>-0.3657</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.162</v>
+        <v>-0.4538</v>
       </c>
       <c r="U11" t="n">
-        <v>0.235</v>
+        <v>0.0882</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.442</v>
+        <v>-4.3526</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8265</v>
+        <v>-5.2674</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3845</v>
+        <v>0.9147</v>
       </c>
       <c r="G12" t="n">
         <v>0.5413</v>
@@ -1390,13 +1390,13 @@
         <v>1.6649</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5023</v>
+        <v>-0.4129</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0967</v>
+        <v>-0.5376</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5945</v>
+        <v>0.1247</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5673</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.381499999999999</v>
+        <v>6.033799999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.177</v>
+        <v>-6.5246</v>
       </c>
       <c r="F13" t="n">
-        <v>12.5583</v>
+        <v>12.5582</v>
       </c>
       <c r="G13" t="n">
         <v>6.429399999999998</v>
@@ -1453,7 +1453,7 @@
         <v>1.5904</v>
       </c>
       <c r="N13" t="n">
-        <v>2.978</v>
+        <v>2.978000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-1.3878</v>
@@ -1468,10 +1468,10 @@
         <v>12.4871</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5525</v>
+        <v>-0.9002999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.7046</v>
+        <v>-2.0521</v>
       </c>
       <c r="U13" t="n">
         <v>1.1522</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0761</v>
+        <v>3.8912</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5325</v>
+        <v>3.1754</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5436</v>
+        <v>0.7158</v>
       </c>
       <c r="G14" t="n">
         <v>3.1684</v>
@@ -1546,13 +1546,13 @@
         <v>0.8325</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6948</v>
+        <v>0.1204</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7177</v>
+        <v>-0.0747</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0229</v>
+        <v>0.1951</v>
       </c>
       <c r="V14" t="n">
         <v>-0.23</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7233</v>
+        <v>2.0749</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8495</v>
+        <v>1.1088</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8737</v>
+        <v>0.9661</v>
       </c>
       <c r="G15" t="n">
-        <v>1.044</v>
+        <v>1.4685</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3902</v>
+        <v>2.2474</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3463</v>
+        <v>-0.7789</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8563</v>
+        <v>1.3175</v>
       </c>
       <c r="K15" t="n">
         <v>1.4923</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.636</v>
+        <v>-0.1747</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1877</v>
+        <v>0.1509</v>
       </c>
       <c r="N15" t="n">
-        <v>0.898</v>
+        <v>0.7551</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7103</v>
+        <v>-0.6041</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6244</v>
+        <v>0.6244</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3037</v>
+        <v>-0.018</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4501</v>
+        <v>-0.3357</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8536</v>
+        <v>0.3178</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5838</v>
+        <v>1.1675</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3235</v>
+        <v>1.5519</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0575</v>
+        <v>0.2066</v>
       </c>
       <c r="F16" t="n">
-        <v>0.266</v>
+        <v>1.3453</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5838</v>
+        <v>1.044</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0596</v>
+        <v>2.3902</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6435</v>
+        <v>-1.3463</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2532</v>
+        <v>0.8563</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0384</v>
+        <v>1.4923</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2148</v>
+        <v>-0.636</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3306</v>
+        <v>0.1877</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.098</v>
+        <v>0.898</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4286</v>
+        <v>-0.7103</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2603</v>
+        <v>1.1323</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1957</v>
+        <v>-0.1928</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0646</v>
+        <v>1.3251</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9661</v>
+        <v>1.4409</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4658</v>
+        <v>1.0575</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5003</v>
+        <v>0.3835</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4685</v>
+        <v>1.5838</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2474</v>
+        <v>-0.0596</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7789</v>
+        <v>1.6435</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3175</v>
+        <v>1.2532</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4923</v>
+        <v>0.0384</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1747</v>
+        <v>1.2148</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1509</v>
+        <v>0.3306</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7551</v>
+        <v>-0.098</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6041</v>
+        <v>0.4286</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6649</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1267</v>
+        <v>-0.1429</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9786</v>
+        <v>-0.1957</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1481</v>
+        <v>0.0529</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. WILLIAMS</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1707</v>
+        <v>0.4078</v>
       </c>
       <c r="E18" t="n">
-        <v>0.654</v>
+        <v>-1.807</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4833</v>
+        <v>2.2148</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2695</v>
+        <v>-1.5126</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7032</v>
+        <v>0.4395</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4336</v>
+        <v>-1.9521</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6575</v>
+        <v>-1.3532</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3809</v>
+        <v>-0.5033</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7234</v>
+        <v>-0.8499</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.388</v>
+        <v>-0.1593</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3223</v>
+        <v>0.9428</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7103</v>
+        <v>-1.1022</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.3299</v>
+        <v>-0.2081</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1926</v>
+        <v>0.2554</v>
       </c>
       <c r="T18" t="n">
-        <v>1.034</v>
+        <v>-0.2457</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1586</v>
+        <v>0.5011</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.0427</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>N. WILLIAMS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2724</v>
+        <v>-0.3929</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0213</v>
+        <v>-0.2032</v>
       </c>
       <c r="F19" t="n">
-        <v>1.749</v>
+        <v>-0.1897</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5126</v>
+        <v>3.2695</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4395</v>
+        <v>4.7032</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9521</v>
+        <v>-1.4336</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3532</v>
+        <v>3.6575</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5033</v>
+        <v>4.3809</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8499</v>
+        <v>-0.7234</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1593</v>
+        <v>-0.388</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9428</v>
+        <v>0.3223</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1022</v>
+        <v>-0.7103</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6649</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2081</v>
+        <v>-3.3299</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8731</v>
+        <v>2.0812</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4247</v>
+        <v>0.6289</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.46</v>
+        <v>0.1767</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0353</v>
+        <v>0.4522</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-3.0427</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7677</v>
+        <v>-1.5875</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6048</v>
+        <v>-0.4358</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8372</v>
+        <v>-1.1517</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.145</v>
+        <v>-2.1632</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.8682</v>
+        <v>-1.177</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2768</v>
+        <v>-0.9862</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.9245</v>
+        <v>-0.7915</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.0028</v>
+        <v>-0.6952</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0784</v>
+        <v>-0.0963</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2206</v>
+        <v>-1.3717</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1346</v>
+        <v>-0.4818</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3551</v>
+        <v>-0.8899</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5449</v>
+        <v>-0.1111</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3602</v>
+        <v>0.1257</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1847</v>
+        <v>-0.2368</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9651</v>
+        <v>-1.9298</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3314</v>
+        <v>-3.7318</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3663</v>
+        <v>1.8021</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1012</v>
+        <v>-1.4703</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1278</v>
+        <v>-4.1791</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9734</v>
+        <v>2.7089</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.1131</v>
+        <v>-0.7311</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2051</v>
+        <v>-4.1135</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.908</v>
+        <v>3.3824</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9881</v>
+        <v>-0.7391</v>
       </c>
       <c r="N21" t="n">
-        <v>0.07729999999999999</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0654</v>
+        <v>-0.6735</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.2487</v>
+        <v>-2.2893</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5337</v>
+        <v>-0.1057</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1371</v>
+        <v>-0.3576</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6708</v>
+        <v>0.2519</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.23</v>
+        <v>-0.3538</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1675</v>
+        <v>-0.3538</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0812</v>
+        <v>-2.1975</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7573</v>
+        <v>-2.4385</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3239</v>
+        <v>0.241</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1632</v>
+        <v>-3.1012</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.177</v>
+        <v>-0.1278</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9862</v>
+        <v>-2.9734</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7915</v>
+        <v>-2.1131</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6952</v>
+        <v>-0.2051</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0963</v>
+        <v>-1.908</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3717</v>
+        <v>-0.9881</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4818</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8899</v>
+        <v>-1.0654</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0406</v>
+        <v>2.0812</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6048</v>
+        <v>0.3012</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1957</v>
+        <v>-0.2442</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4091</v>
+        <v>0.5455</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3538</v>
+        <v>-0.23</v>
       </c>
       <c r="W22" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5838</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6442</v>
+        <v>-2.5408</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1605</v>
+        <v>-4.4621</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5163</v>
+        <v>1.9213</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4703</v>
+        <v>-4.145</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.1791</v>
+        <v>-3.8682</v>
       </c>
       <c r="I23" t="n">
-        <v>2.7089</v>
+        <v>-0.2768</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7311</v>
+        <v>-3.9245</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.1135</v>
+        <v>-4.0028</v>
       </c>
       <c r="L23" t="n">
-        <v>3.3824</v>
+        <v>0.0784</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7391</v>
+        <v>-0.2206</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.1346</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6735</v>
+        <v>-0.3551</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.8325</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2893</v>
+        <v>-1.0406</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2893</v>
+        <v>1.8731</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8201000000000001</v>
+        <v>0.7718</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7862</v>
+        <v>0.503</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0339</v>
+        <v>0.2688</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9106</v>
+        <v>-4.6709</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2424</v>
+        <v>-5.0281</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3318</v>
+        <v>0.3572</v>
       </c>
       <c r="G24" t="n">
         <v>-4.5712</v>
@@ -2326,13 +2326,13 @@
         <v>1.4568</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0907</v>
+        <v>0.1491</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5252</v>
+        <v>-0.3109</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4346</v>
+        <v>0.46</v>
       </c>
       <c r="V24" t="n">
         <v>0.5838</v>
@@ -2359,28 +2359,28 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.381499999999999</v>
+        <v>-3.952699999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.5584</v>
+        <v>-12.5582</v>
       </c>
       <c r="F25" t="n">
-        <v>7.177</v>
+        <v>8.605700000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-6.4293</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.4286</v>
+        <v>-1.428600000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-5.0006</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.590300000000001</v>
+        <v>-1.590299999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.978000000000001</v>
+        <v>-2.978</v>
       </c>
       <c r="L25" t="n">
         <v>1.387900000000001</v>
@@ -2389,10 +2389,10 @@
         <v>-4.839</v>
       </c>
       <c r="N25" t="n">
-        <v>1.549400000000001</v>
+        <v>1.5494</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.388399999999999</v>
+        <v>-6.388400000000001</v>
       </c>
       <c r="P25" t="n">
         <v>3.1218</v>
@@ -2404,13 +2404,13 @@
         <v>15.6089</v>
       </c>
       <c r="S25" t="n">
-        <v>1.5528</v>
+        <v>2.9814</v>
       </c>
       <c r="T25" t="n">
         <v>-1.1519</v>
       </c>
       <c r="U25" t="n">
-        <v>2.7048</v>
+        <v>4.1336</v>
       </c>
       <c r="V25" t="n">
         <v>-3.6265</v>
@@ -2419,7 +2419,7 @@
         <v>2.6712</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.297700000000001</v>
+        <v>-6.2977</v>
       </c>
     </row>
   </sheetData>
